--- a/src/styles/task/Task Template.xlsx
+++ b/src/styles/task/Task Template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6800"/>
+    <workbookView windowWidth="19200" windowHeight="7510" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Tasks" sheetId="1" r:id="rId1"/>
@@ -1116,6 +1116,9 @@
   <sheetPr/>
   <dimension ref="A1:A4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.5" outlineLevelRow="3"/>
+  <cols>
+    <col min="1" max="1" width="136.166666666667" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">

--- a/src/styles/task/Task Template.xlsx
+++ b/src/styles/task/Task Template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7510" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="7510"/>
   </bookViews>
   <sheets>
     <sheet name="Tasks" sheetId="1" r:id="rId1"/>
@@ -28,18 +28,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Title</t>
   </si>
   <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Start Date</t>
-  </si>
-  <si>
-    <t>Start Time</t>
+    <t>Priority</t>
   </si>
   <si>
     <t>End Date</t>
@@ -48,16 +42,78 @@
     <t>End Time</t>
   </si>
   <si>
-    <t>Task template columns: title, description, priority, status, start_date (dd/mm/yyyy), start_time (hh:mm), end_date (dd/mm/yyyy), end_time (hh:mm)</t>
+    <t>Description</t>
   </si>
   <si>
-    <t>priority: high/medium/low; status: pending/completed/overdue</t>
-  </si>
-  <si>
-    <t>Dates must be dd/mm/yyyy. Times must be hh:mm (24h).</t>
-  </si>
-  <si>
-    <t>If end_date is empty, it can be same day as start_date; times are optional.</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Columns:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+title, description, end_date (dd/mm/yyyy), end_time (hh:mm)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Date Format:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+All dates must be in dd/mm/yyyy format.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Time Format:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+All times must be in hh:mm (24-hour) format.
+Times are optional — you can leave them empty for all-day tasks.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -70,8 +126,16 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_-* #,##0\ &quot;₫&quot;_-;\-* #,##0\ &quot;₫&quot;_-;_-* &quot;-&quot;\ &quot;₫&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="22">
-    <font>
+  <fonts count="23">
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -545,154 +609,160 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1076,33 +1146,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.5" outlineLevelCol="5"/>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="4.75" customWidth="1"/>
-    <col min="2" max="2" width="10.8333333333333" customWidth="1"/>
-    <col min="3" max="4" width="10" customWidth="1"/>
-    <col min="5" max="6" width="9.33333333333333" customWidth="1"/>
+    <col min="1" max="1" width="5.08333333333333" customWidth="1"/>
+    <col min="2" max="2" width="6.58333333333333" customWidth="1"/>
+    <col min="3" max="3" width="8.91666666666667" customWidth="1"/>
+    <col min="4" max="4" width="9.08333333333333" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1114,37 +1182,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.5" outlineLevelRow="3"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.5"/>
   <cols>
     <col min="1" max="1" width="136.166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" t="s">
-        <v>9</v>
+    <row r="1" ht="108.5" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:A4" numberStoredAsText="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
--- a/src/styles/task/Task Template.xlsx
+++ b/src/styles/task/Task Template.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
   <si>
     <t>Title</t>
   </si>
@@ -114,6 +114,15 @@
 All times must be in hh:mm (24-hour) format.
 Times are optional — you can leave them empty for all-day tasks.</t>
     </r>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>High</t>
   </si>
 </sst>
 </file>
@@ -759,10 +768,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1157,23 +1166,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B$1:B$1048576">
+      <formula1>Instructions!$D$3:$D$5</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -1182,8 +1196,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.5"/>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.5" outlineLevelRow="4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="136.166666666667" customWidth="1"/>
   </cols>
@@ -1193,6 +1207,26 @@
         <v>5</v>
       </c>
     </row>
+    <row r="2" spans="4:4">
+      <c r="D2" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="4:4">
+      <c r="D3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="4:4">
+      <c r="D4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="4:4">
+      <c r="D5" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
